--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,22 +698,18 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>KHz</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -721,6 +717,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62492.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>UJUBLUI</t>
         </is>
       </c>
     </row>
